--- a/20240322_oliynyk_test/output/20240322_oliynyk_test_site_pairs.xlsx
+++ b/20240322_oliynyk_test/output/20240322_oliynyk_test_site_pairs.xlsx
@@ -7,8 +7,13 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ni-Ga" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ni-Ni" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ga-Ga" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Co-Ga" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dy-Ga" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ni-Ga" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rh-Si" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ni-Ni" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Si-Si" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,28 +454,13 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1830597.cif</t>
+          <t>1633288.cif</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.424</v>
+        <v>2.884</v>
       </c>
       <c r="C2" t="inlineStr">
-        <is>
-          <t>deficiency_no_atomic_mixing</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>1830597.cif</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="C3" t="inlineStr">
         <is>
           <t>full_occupancy</t>
         </is>
@@ -487,6 +477,355 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1633288.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1633288.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2.456</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1633288.cif</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.477</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1633288.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.979</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>1830597.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.424</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>deficiency_no_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1010020.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2.494</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>1830597.cif</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>453819.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2.373</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>453820.cif</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2.382</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>453821.cif</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2.389</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>deficiency_no_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>453821.cif</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2.412</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>453821.cif</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2.414</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>453821.cif</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2.439</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>453821.cif</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2.484</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>453821.cif</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2.523</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>full_occupancy</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
@@ -540,4 +879,50 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Distance</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Atomic Mixing</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>453821.cif</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1.816</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>deficiency_no_atomic_mixing</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/20240322_oliynyk_test/output/20240322_oliynyk_test_site_pairs.xlsx
+++ b/20240322_oliynyk_test/output/20240322_oliynyk_test_site_pairs.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Ni-Ga" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Ni-Ni" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ni-Ga" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ni-Ni" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/20240322_oliynyk_test/output/20240322_oliynyk_test_site_pairs.xlsx
+++ b/20240322_oliynyk_test/output/20240322_oliynyk_test_site_pairs.xlsx
@@ -7,8 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ni-Ga" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ni-Ni" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ni-Ni" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ni-Ga" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,11 +453,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.424</v>
+        <v>2.477</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>deficiency_no_atomic_mixing</t>
+          <t>Full occupancy</t>
         </is>
       </c>
     </row>
@@ -472,9 +472,36 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2.504</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.037</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -487,7 +514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -514,11 +541,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.477</v>
+        <v>2.424</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>full_occupancy</t>
+          <t>Deficiency without atomic mixing</t>
         </is>
       </c>
     </row>
@@ -533,9 +560,36 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>full_occupancy</t>
-        </is>
-      </c>
+          <t>Full occupancy</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Average</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2.477</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>SD</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
